--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788676</v>
+        <v>129788679</v>
       </c>
       <c r="B2" t="n">
         <v>57736</v>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473152</v>
+        <v>473141</v>
       </c>
       <c r="R2" t="n">
-        <v>7028444</v>
+        <v>7028493</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på två granar.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Ringhack på 2 stammar. # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788679</v>
+        <v>129788676</v>
       </c>
       <c r="B3" t="n">
         <v>57736</v>
@@ -847,7 +847,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473141</v>
+        <v>473152</v>
       </c>
       <c r="R3" t="n">
-        <v>7028493</v>
+        <v>7028444</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran nära vägen.</t>
+          <t>Ringhack (savhack), färska och äldre, på två granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +935,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Ringhack på 2 stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,7 +953,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788675</v>
+        <v>129788680</v>
       </c>
       <c r="B4" t="n">
         <v>57736</v>
@@ -986,7 +986,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473154</v>
+        <v>472988</v>
       </c>
       <c r="R4" t="n">
-        <v>7028403</v>
+        <v>7028523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,9 +1067,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1087,7 +1092,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788680</v>
+        <v>129788675</v>
       </c>
       <c r="B5" t="n">
         <v>57736</v>
@@ -1120,7 +1125,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1134,10 +1139,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472988</v>
+        <v>473154</v>
       </c>
       <c r="R5" t="n">
-        <v>7028523</v>
+        <v>7028403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1174,7 +1179,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1201,14 +1206,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788674</v>
+        <v>129788677</v>
       </c>
       <c r="B6" t="n">
         <v>57736</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473156</v>
+        <v>473151</v>
       </c>
       <c r="R6" t="n">
-        <v>7028391</v>
+        <v>7028457</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,7 +1365,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788677</v>
+        <v>129788674</v>
       </c>
       <c r="B7" t="n">
         <v>57736</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473151</v>
+        <v>473156</v>
       </c>
       <c r="R7" t="n">
-        <v>7028457</v>
+        <v>7028391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129788679</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>129788676</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>129788680</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129788675</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>129788677</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>129788674</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>129788678</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129788679</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         <v>129788676</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>129788680</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>129788675</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788677</v>
+        <v>129788674</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473151</v>
+        <v>473156</v>
       </c>
       <c r="R6" t="n">
-        <v>7028457</v>
+        <v>7028391</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788674</v>
+        <v>129788677</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473156</v>
+        <v>473151</v>
       </c>
       <c r="R7" t="n">
-        <v>7028391</v>
+        <v>7028457</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1507,7 +1507,7 @@
         <v>129788678</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -1226,7 +1226,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788674</v>
+        <v>129788677</v>
       </c>
       <c r="B6" t="n">
         <v>57740</v>
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473156</v>
+        <v>473151</v>
       </c>
       <c r="R6" t="n">
-        <v>7028391</v>
+        <v>7028457</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,7 +1365,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788677</v>
+        <v>129788674</v>
       </c>
       <c r="B7" t="n">
         <v>57740</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473151</v>
+        <v>473156</v>
       </c>
       <c r="R7" t="n">
-        <v>7028457</v>
+        <v>7028391</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788679</v>
+        <v>129788674</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473141</v>
+        <v>473156</v>
       </c>
       <c r="R2" t="n">
-        <v>7028493</v>
+        <v>7028391</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran nära vägen.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -814,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788676</v>
+        <v>129788675</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473152</v>
+        <v>473154</v>
       </c>
       <c r="R3" t="n">
-        <v>7028444</v>
+        <v>7028403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på två granar.</t>
+          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,14 +928,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Ringhack på 2 stammar. # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,10 +948,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788680</v>
+        <v>129788676</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,10 +995,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472988</v>
+        <v>473152</v>
       </c>
       <c r="R4" t="n">
-        <v>7028523</v>
+        <v>7028444</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1040,7 +1035,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på två granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1069,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Ringhack på 2 stammar. # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1092,10 +1087,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788675</v>
+        <v>129788677</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,10 +1134,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473154</v>
+        <v>473151</v>
       </c>
       <c r="R5" t="n">
-        <v>7028403</v>
+        <v>7028457</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1179,7 +1174,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1206,9 +1201,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788674</v>
+        <v>129788678</v>
       </c>
       <c r="B6" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1273,10 +1273,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473156</v>
+        <v>473147</v>
       </c>
       <c r="R6" t="n">
-        <v>7028391</v>
+        <v>7028481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran nära vägen.</t>
+          <t>Ringhack (savhack), färska, på en smal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788677</v>
+        <v>129788679</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473151</v>
+        <v>473141</v>
       </c>
       <c r="R7" t="n">
-        <v>7028457</v>
+        <v>7028493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran nära vägen.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1504,10 +1504,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788678</v>
+        <v>129788680</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473147</v>
+        <v>472988</v>
       </c>
       <c r="R8" t="n">
-        <v>7028481</v>
+        <v>7028523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en smal gran.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30771-2023 artfynd.xlsx
+++ b/artfynd/A 30771-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -811,6 +816,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -945,6 +955,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788675</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1084,6 +1099,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788676</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1223,6 +1243,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788677</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1362,6 +1387,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788678</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1501,6 +1531,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788679</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1640,8 +1675,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>